--- a/InputData/elec/RM/Reserve Margin.xlsx
+++ b/InputData/elec/RM/Reserve Margin.xlsx
@@ -1,67 +1,71 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipI - units progress\InputData\elec\RM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\RM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2252071D-D393-47FC-8437-E7879E1328CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="75" windowWidth="22995" windowHeight="11580"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="RM" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>RM Reserve Margin</t>
   </si>
   <si>
+    <t>Iowa</t>
+  </si>
+  <si>
     <t>Source:</t>
   </si>
   <si>
     <t xml:space="preserve">North American Electrict Reliability Coorporation </t>
   </si>
   <si>
+    <t>2015 Summer Reliability Assessment</t>
+  </si>
+  <si>
     <t>http://www.nerc.com/pa/RAPA/ra/Reliability%20Assessments%20DL/2015_Summer_Reliability_Assessment.pdf</t>
   </si>
   <si>
     <t>p.3, Table 1: Projected Demand, Resources, and Planning Reserve Margins, NERC Reference Margin Level (%)</t>
   </si>
   <si>
-    <t>2015 Summer Reliability Assessment</t>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The reserve margin (difference between the total generation available and the forecasted peak demand) in the U.S. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dataset doesn't vary by year, but the RM Reserve Margin variable is a time series to support countries that project </t>
+  </si>
+  <si>
+    <t>changes in future reserve margin by year.</t>
+  </si>
+  <si>
+    <t>(dimensionless)</t>
   </si>
   <si>
     <t>Reserve Margin</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The reserve margin (difference between the total generation available and the forecasted peak demand) in the U.S. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dataset doesn't vary by year, but the RM Reserve Margin variable is a time series to support countries that project </t>
-  </si>
-  <si>
-    <t>changes in future reserve margin by year.</t>
-  </si>
-  <si>
-    <t>(dimensionless)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -99,13 +103,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -409,81 +412,84 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
         <v>2015</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AK2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -596,116 +602,116 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="C2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="G2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="H2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="I2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="J2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="K2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="L2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="M2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="N2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="O2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="P2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="R2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="S2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="T2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="U2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="V2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="W2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="X2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="Y2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="Z2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AA2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AB2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AC2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AD2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AE2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AF2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AG2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AH2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AI2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AJ2" s="3">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AK2" s="3">
+        <v>12</v>
+      </c>
+      <c r="B2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="C2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="D2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="E2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="F2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="G2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="H2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="I2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="J2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="K2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="L2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="M2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="N2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="O2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="P2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="Q2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="R2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="S2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="T2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="U2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="V2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="W2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="X2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="Y2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="Z2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AA2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AB2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AC2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AD2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AE2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AF2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AG2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AH2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AI2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AJ2">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AK2">
         <v>0.14119999999999999</v>
       </c>
     </row>

--- a/InputData/elec/RM/Reserve Margin.xlsx
+++ b/InputData/elec/RM/Reserve Margin.xlsx
@@ -1,47 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\RM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipI - units progress\InputData\elec\RM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2252071D-D393-47FC-8437-E7879E1328CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="75" windowWidth="22995" windowHeight="11580"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="RM" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>RM Reserve Margin</t>
   </si>
   <si>
-    <t>Iowa</t>
-  </si>
-  <si>
     <t>Source:</t>
   </si>
   <si>
     <t xml:space="preserve">North American Electrict Reliability Coorporation </t>
   </si>
   <si>
+    <t>http://www.nerc.com/pa/RAPA/ra/Reliability%20Assessments%20DL/2015_Summer_Reliability_Assessment.pdf</t>
+  </si>
+  <si>
+    <t>p.3, Table 1: Projected Demand, Resources, and Planning Reserve Margins, NERC Reference Margin Level (%)</t>
+  </si>
+  <si>
     <t>2015 Summer Reliability Assessment</t>
   </si>
   <si>
-    <t>http://www.nerc.com/pa/RAPA/ra/Reliability%20Assessments%20DL/2015_Summer_Reliability_Assessment.pdf</t>
-  </si>
-  <si>
-    <t>p.3, Table 1: Projected Demand, Resources, and Planning Reserve Margins, NERC Reference Margin Level (%)</t>
+    <t>Reserve Margin</t>
   </si>
   <si>
     <t>Notes</t>
@@ -57,15 +56,12 @@
   </si>
   <si>
     <t>(dimensionless)</t>
-  </si>
-  <si>
-    <t>Reserve Margin</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -103,12 +99,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -412,84 +409,81 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B4" s="2">
         <v>2015</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AK2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -602,116 +596,116 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="C2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="D2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="E2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="F2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="G2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="H2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="I2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="J2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="K2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="L2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="M2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="N2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="O2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="P2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="Q2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="R2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="S2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="T2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="U2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="V2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="W2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="X2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="Y2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="Z2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AA2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AB2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AC2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AD2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AE2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AF2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AG2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AH2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AI2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AJ2">
-        <v>0.14119999999999999</v>
-      </c>
-      <c r="AK2">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="K2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="L2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="M2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="N2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="O2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="P2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="R2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="S2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="T2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="U2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="V2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="W2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="X2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="Y2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="Z2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AA2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AD2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AE2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AF2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AG2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AH2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AI2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AJ2" s="3">
+        <v>0.14119999999999999</v>
+      </c>
+      <c r="AK2" s="3">
         <v>0.14119999999999999</v>
       </c>
     </row>
